--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_MOLINA OLEA CB COSTA MOTRIL.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_MOLINA OLEA CB COSTA MOTRIL.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. BUALÓ</t>
+          <t>A. BUALO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>21</v>
       </c>
       <c r="D2" t="n">
-        <v>31.7161</v>
+        <v>37.3255</v>
       </c>
       <c r="E2" t="n">
-        <v>31.7161</v>
+        <v>36.9757</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.3498999999999997</v>
       </c>
       <c r="G2" t="n">
-        <v>31.7161</v>
+        <v>11.1858</v>
       </c>
       <c r="H2" t="n">
-        <v>17.252</v>
+        <v>1.4532</v>
       </c>
       <c r="I2" t="n">
-        <v>14.4641</v>
+        <v>9.7326</v>
       </c>
       <c r="J2" t="n">
-        <v>31.7161</v>
+        <v>49.16</v>
       </c>
       <c r="K2" t="n">
-        <v>17.252</v>
+        <v>23.6836</v>
       </c>
       <c r="L2" t="n">
-        <v>14.4641</v>
+        <v>25.4768</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>-37.974</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-22.2302</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>-15.7442</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-5.153699999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-51.7361</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>46.5826</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>-11.3247</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>-13.883</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.5584</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>42.6179</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>53.4345</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-10.817</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. BUALO</t>
+          <t>A. BUALÓ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>28.8374</v>
+        <v>31.7161</v>
       </c>
       <c r="E3" t="n">
-        <v>28.6758</v>
+        <v>31.7161</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1614999999999989</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>11.1858</v>
+        <v>31.7161</v>
       </c>
       <c r="H3" t="n">
-        <v>1.4532</v>
+        <v>17.252</v>
       </c>
       <c r="I3" t="n">
-        <v>9.7326</v>
+        <v>14.4641</v>
       </c>
       <c r="J3" t="n">
-        <v>49.16</v>
+        <v>31.7161</v>
       </c>
       <c r="K3" t="n">
-        <v>23.6836</v>
+        <v>17.252</v>
       </c>
       <c r="L3" t="n">
-        <v>25.4768</v>
+        <v>14.4641</v>
       </c>
       <c r="M3" t="n">
-        <v>-37.974</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-22.2302</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-15.7442</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-5.153699999999999</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-51.7361</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>46.5826</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-19.8126</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-22.1826</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.3702</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>42.6179</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>53.4345</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-10.817</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>27.6507</v>
+        <v>25.1527</v>
       </c>
       <c r="E4" t="n">
-        <v>39.0197</v>
+        <v>32.6506</v>
       </c>
       <c r="F4" t="n">
-        <v>-11.3695</v>
+        <v>-7.4978</v>
       </c>
       <c r="G4" t="n">
         <v>-3.1195</v>
@@ -766,13 +766,13 @@
         <v>50.9433</v>
       </c>
       <c r="S4" t="n">
-        <v>-7.306</v>
+        <v>-9.803700000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-2.351800000000001</v>
+        <v>-8.7211</v>
       </c>
       <c r="U4" t="n">
-        <v>-4.9539</v>
+        <v>-1.0823</v>
       </c>
       <c r="V4" t="n">
         <v>39.4636</v>
@@ -799,13 +799,13 @@
         <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>5.5208</v>
+        <v>6.0573</v>
       </c>
       <c r="E5" t="n">
-        <v>10.1283</v>
+        <v>8.0581</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.607300000000001</v>
+        <v>-2.0008</v>
       </c>
       <c r="G5" t="n">
         <v>3.9304</v>
@@ -844,13 +844,13 @@
         <v>12.2897</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.09570000000000012</v>
+        <v>0.4407000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1849</v>
+        <v>-1.8858</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2804</v>
+        <v>2.3262</v>
       </c>
       <c r="V5" t="n">
         <v>-3.071</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. GARCIA GUERRERO</t>
+          <t>J. MOLINA VERA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>3.0994</v>
+        <v>0.9596</v>
       </c>
       <c r="E6" t="n">
-        <v>3.0505</v>
+        <v>-0.0262</v>
       </c>
       <c r="F6" t="n">
-        <v>0.04879999999999973</v>
+        <v>0.9857</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.073100000000001</v>
+        <v>1.3615</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7477000000000003</v>
+        <v>1.0842</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.8208</v>
+        <v>0.2773</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7835</v>
+        <v>0.9484</v>
       </c>
       <c r="K6" t="n">
-        <v>3.4443</v>
+        <v>0.9484</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.6601</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-4.857</v>
+        <v>0.4131000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.6961</v>
+        <v>0.1358</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.1609</v>
+        <v>0.2773</v>
       </c>
       <c r="P6" t="n">
-        <v>6.9376</v>
+        <v>-0.5947000000000001</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R6" t="n">
-        <v>7.9287</v>
+        <v>0.3964</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.1927</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0505</v>
+        <v>0.01650000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2388999999999999</v>
+        <v>0.1762</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.5774</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.7845</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. MOLINA VERA</t>
+          <t>A. GARCIA GUERRERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7558</v>
+        <v>0.7236999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2299</v>
+        <v>1.3251</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9858</v>
+        <v>-0.6015000000000003</v>
       </c>
       <c r="G7" t="n">
-        <v>1.3615</v>
+        <v>-3.073100000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0842</v>
+        <v>0.7477000000000003</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2773</v>
+        <v>-3.8208</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9484</v>
+        <v>1.7835</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9484</v>
+        <v>3.4443</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-1.6601</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4131000000000001</v>
+        <v>-4.857</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1358</v>
+        <v>-2.6961</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2773</v>
+        <v>-2.1609</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.5947000000000001</v>
+        <v>6.9376</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3964</v>
+        <v>7.9287</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01110000000000001</v>
+        <v>-1.5636</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1872</v>
+        <v>-0.6747999999999998</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1761</v>
+        <v>-0.8891</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.5774</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.7845</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1301</v>
+        <v>-0.5095000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0793</v>
+        <v>-0.4867</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.05080000000000001</v>
+        <v>-0.02270000000000003</v>
       </c>
       <c r="G8" t="n">
         <v>-0.4991</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.0429</v>
+        <v>0.6635</v>
       </c>
       <c r="T8" t="n">
-        <v>1.2335</v>
+        <v>0.826</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1905</v>
+        <v>-0.1625</v>
       </c>
       <c r="V8" t="n">
         <v>-0.674</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ MORENO</t>
+          <t>F. MARIN FERRES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9298</v>
+        <v>-1.5227</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-2.5292</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.09660000000000024</v>
+        <v>1.0067</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3613</v>
+        <v>-1.412</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3351000000000001</v>
+        <v>-3.0113</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6966</v>
+        <v>1.5993</v>
       </c>
       <c r="J9" t="n">
-        <v>0.05830000000000013</v>
+        <v>-1.9727</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6532</v>
+        <v>-2.6156</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5949</v>
+        <v>0.6428</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4197000000000001</v>
+        <v>0.5608000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3179</v>
+        <v>-0.3956999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1017</v>
+        <v>0.9565</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.5946</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.1715</v>
+        <v>-1.1893</v>
       </c>
       <c r="R9" t="n">
-        <v>2.5769</v>
+        <v>0.5946</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2364</v>
+        <v>0.2176</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5397999999999999</v>
+        <v>0.3663</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6964000000000001</v>
+        <v>-0.1488</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2101</v>
+        <v>0.2666</v>
       </c>
       <c r="W9" t="n">
-        <v>1.7403</v>
+        <v>0.2666</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.9504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. MARIN FERRES</t>
+          <t>J. FERNANDEZ MORENO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4978</v>
+        <v>-1.8404</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2236</v>
+        <v>-1.6875</v>
       </c>
       <c r="F10" t="n">
-        <v>0.726</v>
+        <v>-0.1527000000000003</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.412</v>
+        <v>-0.3613</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.0113</v>
+        <v>0.3351000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5993</v>
+        <v>-0.6966</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.9727</v>
+        <v>0.05830000000000013</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.6156</v>
+        <v>0.6532</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6428</v>
+        <v>-0.5949</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5608000000000001</v>
+        <v>-0.4197000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3956999999999999</v>
+        <v>-0.3179</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9565</v>
+        <v>-0.1017</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.5947</v>
+        <v>-0.5946</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1893</v>
+        <v>-3.1715</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5946</v>
+        <v>2.5769</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2423</v>
+        <v>0.3258</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6718</v>
+        <v>-0.3146</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4295</v>
+        <v>0.6404000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2666</v>
+        <v>-1.2101</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2666</v>
+        <v>1.7403</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-2.9504</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. MARIN FERRES</t>
+          <t>A. MARTINEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1413</v>
+        <v>-1.9322</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1874</v>
+        <v>0.1747000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0461</v>
+        <v>-2.1068</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.659</v>
+        <v>-2.4734</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2023</v>
+        <v>-0.9716</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5433</v>
+        <v>-1.5019</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.3381</v>
+        <v>0.5508</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.3381</v>
+        <v>0.4911999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.05959999999999988</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6791</v>
+        <v>-3.0242</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1358</v>
+        <v>-1.4628</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5433</v>
+        <v>-1.5615</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.7929</v>
+        <v>-0.1982999999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1982</v>
+        <v>1.784</v>
       </c>
       <c r="S11" t="n">
-        <v>0.251</v>
+        <v>0.09359999999999996</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1248</v>
+        <v>0.1323</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3758</v>
+        <v>-0.0388</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9405</v>
+        <v>0.6458</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2666</v>
+        <v>1.4737</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2071</v>
+        <v>-0.8279</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. MARTINEZ GONZALEZ</t>
+          <t>E. MARIN FERRES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.691</v>
+        <v>-2.3098</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6403999999999999</v>
+        <v>-2.1874</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0507</v>
+        <v>-0.1224</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.4734</v>
+        <v>-0.659</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.9716</v>
+        <v>-1.2023</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.5019</v>
+        <v>0.5433</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5508</v>
+        <v>-1.3381</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4911999999999999</v>
+        <v>-1.3381</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05959999999999988</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.0242</v>
+        <v>0.6791</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.4628</v>
+        <v>0.1358</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.5615</v>
+        <v>0.5433</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1982999999999999</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R12" t="n">
-        <v>1.784</v>
+        <v>0.1982</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6651999999999999</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6826</v>
+        <v>-0.1248</v>
       </c>
       <c r="U12" t="n">
-        <v>0.01730000000000004</v>
+        <v>0.2074</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6458</v>
+        <v>-0.9405</v>
       </c>
       <c r="W12" t="n">
-        <v>1.4737</v>
+        <v>0.2666</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.8279</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.8251</v>
+        <v>-4.561100000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.706</v>
+        <v>-0.8909999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.1193</v>
+        <v>-3.67</v>
       </c>
       <c r="G13" t="n">
         <v>0.4785999999999999</v>
@@ -1468,13 +1468,13 @@
         <v>2.3786</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.0592</v>
+        <v>-1.7949</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.9858</v>
+        <v>-1.1707</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.0735</v>
+        <v>-0.6243000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-4.6322</v>
@@ -1501,13 +1501,13 @@
         <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.02</v>
+        <v>-4.614799999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.0416</v>
+        <v>-0.3054999999999997</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.9784</v>
+        <v>-4.3092</v>
       </c>
       <c r="G14" t="n">
         <v>-1.9441</v>
@@ -1546,13 +1546,13 @@
         <v>2.7751</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.4487</v>
+        <v>-1.0433</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9322999999999999</v>
+        <v>-0.1960999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.5166</v>
+        <v>-0.8473000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>0.5532000000000001</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>H. FERNANDEZ CAMPOS</t>
+          <t>P. VILLANUEVA LAZARO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>-11.9835</v>
+        <v>-13.2859</v>
       </c>
       <c r="E15" t="n">
-        <v>-5.9006</v>
+        <v>-12.5387</v>
       </c>
       <c r="F15" t="n">
-        <v>-6.082800000000001</v>
+        <v>-0.7471</v>
       </c>
       <c r="G15" t="n">
-        <v>-20.9924</v>
+        <v>-13.9302</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.4901</v>
+        <v>-10.3567</v>
       </c>
       <c r="I15" t="n">
-        <v>-19.5024</v>
+        <v>-3.5735</v>
       </c>
       <c r="J15" t="n">
-        <v>3.688</v>
+        <v>-5.2117</v>
       </c>
       <c r="K15" t="n">
-        <v>5.7913</v>
+        <v>-4.8514</v>
       </c>
       <c r="L15" t="n">
-        <v>-2.1034</v>
+        <v>-0.3603000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-24.6801</v>
+        <v>-8.718500000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>-7.2812</v>
+        <v>-5.5054</v>
       </c>
       <c r="O15" t="n">
-        <v>-17.3988</v>
+        <v>-3.2132</v>
       </c>
       <c r="P15" t="n">
-        <v>6.9377</v>
+        <v>-0.5945999999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>-17.4434</v>
+        <v>-12.8845</v>
       </c>
       <c r="R15" t="n">
-        <v>24.3815</v>
+        <v>12.2898</v>
       </c>
       <c r="S15" t="n">
-        <v>5.6813</v>
+        <v>-1.638</v>
       </c>
       <c r="T15" t="n">
-        <v>3.4492</v>
+        <v>-1.1369</v>
       </c>
       <c r="U15" t="n">
-        <v>2.2322</v>
+        <v>-0.5010000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>-3.6102</v>
+        <v>2.8769</v>
       </c>
       <c r="W15" t="n">
-        <v>4.4061</v>
+        <v>6.6944</v>
       </c>
       <c r="X15" t="n">
-        <v>-8.0162</v>
+        <v>-3.8175</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. VILLANUEVA LAZARO</t>
+          <t>H. FERNANDEZ CAMPOS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D16" t="n">
-        <v>-15.9542</v>
+        <v>-15.8053</v>
       </c>
       <c r="E16" t="n">
-        <v>-15.1084</v>
+        <v>-10.0086</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8457000000000001</v>
+        <v>-5.796600000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>-13.9302</v>
+        <v>-20.9924</v>
       </c>
       <c r="H16" t="n">
-        <v>-10.3567</v>
+        <v>-1.4901</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.5735</v>
+        <v>-19.5024</v>
       </c>
       <c r="J16" t="n">
-        <v>-5.2117</v>
+        <v>3.688</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.8514</v>
+        <v>5.7913</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.3603000000000001</v>
+        <v>-2.1034</v>
       </c>
       <c r="M16" t="n">
-        <v>-8.718500000000001</v>
+        <v>-24.6801</v>
       </c>
       <c r="N16" t="n">
-        <v>-5.5054</v>
+        <v>-7.2812</v>
       </c>
       <c r="O16" t="n">
-        <v>-3.2132</v>
+        <v>-17.3988</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.5945999999999999</v>
+        <v>6.9377</v>
       </c>
       <c r="Q16" t="n">
-        <v>-12.8845</v>
+        <v>-17.4434</v>
       </c>
       <c r="R16" t="n">
-        <v>12.2898</v>
+        <v>24.3815</v>
       </c>
       <c r="S16" t="n">
-        <v>-4.3063</v>
+        <v>1.8591</v>
       </c>
       <c r="T16" t="n">
-        <v>-3.7066</v>
+        <v>-0.6587000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5995999999999999</v>
+        <v>2.5183</v>
       </c>
       <c r="V16" t="n">
-        <v>2.8769</v>
+        <v>-3.6102</v>
       </c>
       <c r="W16" t="n">
-        <v>6.6944</v>
+        <v>4.4061</v>
       </c>
       <c r="X16" t="n">
-        <v>-3.8175</v>
+        <v>-8.0162</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>15</v>
       </c>
       <c r="D17" t="n">
-        <v>-20.4126</v>
+        <v>-21.9111</v>
       </c>
       <c r="E17" t="n">
-        <v>-6.9255</v>
+        <v>-9.561400000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>-13.4871</v>
+        <v>-12.3497</v>
       </c>
       <c r="G17" t="n">
         <v>-11.9002</v>
@@ -1780,13 +1780,13 @@
         <v>12.8844</v>
       </c>
       <c r="S17" t="n">
-        <v>3.0567</v>
+        <v>1.5584</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3987</v>
+        <v>-0.2371</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6582</v>
+        <v>1.7957</v>
       </c>
       <c r="V17" t="n">
         <v>-10.7765</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. HUNT</t>
+          <t>P. FERNANDEZ ANTUNEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D18" t="n">
-        <v>-32.2375</v>
+        <v>-27.2023</v>
       </c>
       <c r="E18" t="n">
-        <v>-21.9484</v>
+        <v>-9.659199999999998</v>
       </c>
       <c r="F18" t="n">
-        <v>-10.2892</v>
+        <v>-17.5432</v>
       </c>
       <c r="G18" t="n">
-        <v>-14.0526</v>
+        <v>-7.7192</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.615999999999999</v>
+        <v>-9.174300000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>-12.4365</v>
+        <v>1.4552</v>
       </c>
       <c r="J18" t="n">
-        <v>9.120999999999999</v>
+        <v>24.9933</v>
       </c>
       <c r="K18" t="n">
-        <v>8.3696</v>
+        <v>5.0936</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7516000000000005</v>
+        <v>19.8999</v>
       </c>
       <c r="M18" t="n">
-        <v>-23.1734</v>
+        <v>-32.7126</v>
       </c>
       <c r="N18" t="n">
-        <v>-9.985200000000001</v>
+        <v>-14.2682</v>
       </c>
       <c r="O18" t="n">
-        <v>-13.1883</v>
+        <v>-18.4445</v>
       </c>
       <c r="P18" t="n">
-        <v>-4.7573</v>
+        <v>2.9732</v>
       </c>
       <c r="Q18" t="n">
-        <v>-31.5174</v>
+        <v>-32.9047</v>
       </c>
       <c r="R18" t="n">
-        <v>26.7601</v>
+        <v>35.8783</v>
       </c>
       <c r="S18" t="n">
-        <v>-7.9524</v>
+        <v>-7.3564</v>
       </c>
       <c r="T18" t="n">
-        <v>-13.4587</v>
+        <v>-9.5787</v>
       </c>
       <c r="U18" t="n">
-        <v>5.5064</v>
+        <v>2.2222</v>
       </c>
       <c r="V18" t="n">
-        <v>-5.4752</v>
+        <v>-15.1</v>
       </c>
       <c r="W18" t="n">
-        <v>13.9071</v>
+        <v>7.8311</v>
       </c>
       <c r="X18" t="n">
-        <v>-19.3823</v>
+        <v>-22.9312</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ ANTUNEZ</t>
+          <t>B. HUNT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,70 +1888,70 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D19" t="n">
-        <v>-32.7119</v>
+        <v>-29.7155</v>
       </c>
       <c r="E19" t="n">
-        <v>-14.8967</v>
+        <v>-17.7755</v>
       </c>
       <c r="F19" t="n">
-        <v>-17.8152</v>
+        <v>-11.94</v>
       </c>
       <c r="G19" t="n">
-        <v>-7.7192</v>
+        <v>-14.0526</v>
       </c>
       <c r="H19" t="n">
-        <v>-9.174300000000001</v>
+        <v>-1.615999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4552</v>
+        <v>-12.4365</v>
       </c>
       <c r="J19" t="n">
-        <v>24.9933</v>
+        <v>9.120999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>5.0936</v>
+        <v>8.3696</v>
       </c>
       <c r="L19" t="n">
-        <v>19.8999</v>
+        <v>0.7516000000000005</v>
       </c>
       <c r="M19" t="n">
-        <v>-32.7126</v>
+        <v>-23.1734</v>
       </c>
       <c r="N19" t="n">
-        <v>-14.2682</v>
+        <v>-9.985200000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>-18.4445</v>
+        <v>-13.1883</v>
       </c>
       <c r="P19" t="n">
-        <v>2.9732</v>
+        <v>-4.7573</v>
       </c>
       <c r="Q19" t="n">
-        <v>-32.9047</v>
+        <v>-31.5174</v>
       </c>
       <c r="R19" t="n">
-        <v>35.8783</v>
+        <v>26.7601</v>
       </c>
       <c r="S19" t="n">
-        <v>-12.8663</v>
+        <v>-5.4305</v>
       </c>
       <c r="T19" t="n">
-        <v>-14.8159</v>
+        <v>-9.286</v>
       </c>
       <c r="U19" t="n">
-        <v>1.9501</v>
+        <v>3.8556</v>
       </c>
       <c r="V19" t="n">
-        <v>-15.1</v>
+        <v>-5.4752</v>
       </c>
       <c r="W19" t="n">
-        <v>7.8311</v>
+        <v>13.9071</v>
       </c>
       <c r="X19" t="n">
-        <v>-22.9312</v>
+        <v>-19.3823</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>23</v>
       </c>
       <c r="D20" t="n">
-        <v>-40.4636</v>
+        <v>-41.6063</v>
       </c>
       <c r="E20" t="n">
-        <v>-43.6335</v>
+        <v>-40.4107</v>
       </c>
       <c r="F20" t="n">
-        <v>3.169500000000002</v>
+        <v>-1.1956</v>
       </c>
       <c r="G20" t="n">
         <v>-21.1517</v>
@@ -2014,13 +2014,13 @@
         <v>43.4107</v>
       </c>
       <c r="S20" t="n">
-        <v>-4.3616</v>
+        <v>-5.5038</v>
       </c>
       <c r="T20" t="n">
-        <v>-13.7103</v>
+        <v>-10.4877</v>
       </c>
       <c r="U20" t="n">
-        <v>9.3489</v>
+        <v>4.9839</v>
       </c>
       <c r="V20" t="n">
         <v>0.3126999999999999</v>
@@ -2047,13 +2047,13 @@
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>-43.9607</v>
+        <v>-43.4441</v>
       </c>
       <c r="E21" t="n">
-        <v>-21.3583</v>
+        <v>-23.4493</v>
       </c>
       <c r="F21" t="n">
-        <v>-22.6025</v>
+        <v>-19.9947</v>
       </c>
       <c r="G21" t="n">
         <v>-22.9668</v>
@@ -2092,13 +2092,13 @@
         <v>49.754</v>
       </c>
       <c r="S21" t="n">
-        <v>-11.2875</v>
+        <v>-10.7709</v>
       </c>
       <c r="T21" t="n">
-        <v>-8.552200000000001</v>
+        <v>-10.6432</v>
       </c>
       <c r="U21" t="n">
-        <v>-2.7352</v>
+        <v>-0.1279999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>-27.7444</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. GARZON ALVAREZ</t>
+          <t>M. PEREZ SARRABLO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2122,76 +2122,76 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D22" t="n">
-        <v>-56.4427</v>
+        <v>-48.851</v>
       </c>
       <c r="E22" t="n">
-        <v>-30.8141</v>
+        <v>-35.2756</v>
       </c>
       <c r="F22" t="n">
-        <v>-25.6286</v>
+        <v>-13.5752</v>
       </c>
       <c r="G22" t="n">
-        <v>-56.574</v>
+        <v>-28.8479</v>
       </c>
       <c r="H22" t="n">
-        <v>-29.2954</v>
+        <v>-7.669</v>
       </c>
       <c r="I22" t="n">
-        <v>-27.2787</v>
+        <v>-21.1786</v>
       </c>
       <c r="J22" t="n">
-        <v>-11.044</v>
+        <v>7.887599999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>-5.508400000000001</v>
+        <v>9.280899999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>-5.5354</v>
+        <v>-1.3933</v>
       </c>
       <c r="M22" t="n">
-        <v>-45.5303</v>
+        <v>-36.7358</v>
       </c>
       <c r="N22" t="n">
-        <v>-23.7871</v>
+        <v>-16.9502</v>
       </c>
       <c r="O22" t="n">
-        <v>-21.7433</v>
+        <v>-19.7856</v>
       </c>
       <c r="P22" t="n">
-        <v>15.4615</v>
+        <v>3.1717</v>
       </c>
       <c r="Q22" t="n">
-        <v>-28.742</v>
+        <v>-38.0584</v>
       </c>
       <c r="R22" t="n">
-        <v>44.2037</v>
+        <v>41.2302</v>
       </c>
       <c r="S22" t="n">
-        <v>-9.290800000000001</v>
+        <v>-9.915500000000002</v>
       </c>
       <c r="T22" t="n">
-        <v>-7.3489</v>
+        <v>-7.6294</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.9414</v>
+        <v>-2.2859</v>
       </c>
       <c r="V22" t="n">
-        <v>-6.0395</v>
+        <v>-13.2592</v>
       </c>
       <c r="W22" t="n">
-        <v>16.3212</v>
+        <v>2.5248</v>
       </c>
       <c r="X22" t="n">
-        <v>-22.3607</v>
+        <v>-15.7841</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. PEREZ SARRABLO</t>
+          <t>D. GARZON ALVAREZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2200,70 +2200,70 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D23" t="n">
-        <v>-58.371</v>
+        <v>-53.928</v>
       </c>
       <c r="E23" t="n">
-        <v>-41.1077</v>
+        <v>-30.6079</v>
       </c>
       <c r="F23" t="n">
-        <v>-17.2632</v>
+        <v>-23.3202</v>
       </c>
       <c r="G23" t="n">
-        <v>-28.8479</v>
+        <v>-56.574</v>
       </c>
       <c r="H23" t="n">
-        <v>-7.669</v>
+        <v>-29.2954</v>
       </c>
       <c r="I23" t="n">
-        <v>-21.1786</v>
+        <v>-27.2787</v>
       </c>
       <c r="J23" t="n">
-        <v>7.887599999999999</v>
+        <v>-11.044</v>
       </c>
       <c r="K23" t="n">
-        <v>9.280899999999999</v>
+        <v>-5.508400000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.3933</v>
+        <v>-5.5354</v>
       </c>
       <c r="M23" t="n">
-        <v>-36.7358</v>
+        <v>-45.5303</v>
       </c>
       <c r="N23" t="n">
-        <v>-16.9502</v>
+        <v>-23.7871</v>
       </c>
       <c r="O23" t="n">
-        <v>-19.7856</v>
+        <v>-21.7433</v>
       </c>
       <c r="P23" t="n">
-        <v>3.1717</v>
+        <v>15.4615</v>
       </c>
       <c r="Q23" t="n">
-        <v>-38.0584</v>
+        <v>-28.742</v>
       </c>
       <c r="R23" t="n">
-        <v>41.2302</v>
+        <v>44.2037</v>
       </c>
       <c r="S23" t="n">
-        <v>-19.4355</v>
+        <v>-6.776199999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-13.4616</v>
+        <v>-7.1427</v>
       </c>
       <c r="U23" t="n">
-        <v>-5.9742</v>
+        <v>0.3667</v>
       </c>
       <c r="V23" t="n">
-        <v>-13.2592</v>
+        <v>-6.0395</v>
       </c>
       <c r="W23" t="n">
-        <v>2.5248</v>
+        <v>16.3212</v>
       </c>
       <c r="X23" t="n">
-        <v>-15.7841</v>
+        <v>-22.3607</v>
       </c>
     </row>
     <row r="24">
@@ -2281,19 +2281,19 @@
         <v>26</v>
       </c>
       <c r="D24" t="n">
-        <v>-234.1926</v>
+        <v>-211.1051</v>
       </c>
       <c r="E24" t="n">
-        <v>-98.04419999999999</v>
+        <v>-86.5001</v>
       </c>
       <c r="F24" t="n">
-        <v>-136.1492</v>
+        <v>-124.6039</v>
       </c>
       <c r="G24" t="n">
         <v>-163.0041</v>
       </c>
       <c r="H24" t="n">
-        <v>-49.94199999999999</v>
+        <v>-49.94200000000001</v>
       </c>
       <c r="I24" t="n">
         <v>-113.063</v>
@@ -2305,10 +2305,10 @@
         <v>136.1235</v>
       </c>
       <c r="L24" t="n">
-        <v>69.22620000000002</v>
+        <v>69.22620000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>-368.3519000000001</v>
+        <v>-368.3519</v>
       </c>
       <c r="N24" t="n">
         <v>-186.064</v>
@@ -2323,19 +2323,19 @@
         <v>-392.4785</v>
       </c>
       <c r="R24" t="n">
-        <v>419.2408000000001</v>
+        <v>419.2408</v>
       </c>
       <c r="S24" t="n">
-        <v>-90.5763</v>
+        <v>-67.4875</v>
       </c>
       <c r="T24" t="n">
-        <v>-93.97290000000001</v>
+        <v>-82.4302</v>
       </c>
       <c r="U24" t="n">
-        <v>3.3979</v>
+        <v>14.943</v>
       </c>
       <c r="V24" t="n">
-        <v>-7.373500000000003</v>
+        <v>-7.373499999999996</v>
       </c>
       <c r="W24" t="n">
         <v>183.0636</v>
